--- a/data/trans_bre/P15B_3_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P15B_3_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-12,66</t>
+          <t>-11,79</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-43,79%</t>
+          <t>-42,73%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-28,94; -5,37</t>
+          <t>-30,49; -5,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,87; 4,61</t>
+          <t>-13,41; 4,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 27,44</t>
+          <t>-2,22; 30,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-61,29; 24,84</t>
+          <t>-57,02; 19,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-26,66</t>
+          <t>-26,74</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-77,53%</t>
+          <t>-79,32%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 25,58</t>
+          <t>-31,49; 24,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-27,31; 2,36</t>
+          <t>-28,21; 2,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-25,89; 12,7</t>
+          <t>-23,7; 15,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,69; 3,62</t>
+          <t>-51,63; -0,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,94; 132,99</t>
+          <t>-72,79; 120,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,1; 17,06</t>
+          <t>-90,53; 22,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-82,71; 83,29</t>
+          <t>-81,42; 97,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 166,69</t>
+          <t>-100,0; 220,26</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-14,49</t>
+          <t>-14,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-60,0%</t>
+          <t>-60,67%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-68,84; -5,17</t>
+          <t>-66,18; -0,82</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-32,59; -2,34</t>
+          <t>-31,84; -2,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 2,35</t>
+          <t>-35,88; -0,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,98; 1,51</t>
+          <t>-32,76; 3,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 26,64</t>
+          <t>-100,0; 12,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 13,52</t>
+          <t>-100,0; 27,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 59,59</t>
+          <t>-100,0; 50,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-91,05; 27,26</t>
+          <t>-90,11; 60,12</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-17,14</t>
+          <t>-16,99</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-67,84%</t>
+          <t>-68,86%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-75,56; 3,13</t>
+          <t>-73,79; -0,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-50,72; -9,8</t>
+          <t>-51,67; -9,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-31,7; 9,79</t>
+          <t>-31,73; 13,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -1,36</t>
+          <t>-31,87; -4,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 9,79</t>
+          <t>-100,0; 1,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-93,15; -25,47</t>
+          <t>-100,0; -17,58</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,98</t>
+          <t>-100,0; 224,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,72; -1,47</t>
+          <t>-91,91; -5,96</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-15,38</t>
+          <t>-12,98</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-48,47%</t>
+          <t>-44,73%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 0,0</t>
+          <t>-57,57; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-74,06; -17,51</t>
+          <t>-74,32; -16,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 17,7</t>
+          <t>-22,13; 17,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-36,53; 1,45</t>
+          <t>-33,74; 5,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-100,0; -38,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-78,72; 15,25</t>
+          <t>-77,86; 40,28</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-3,93</t>
+          <t>-3,76</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-72,5%</t>
+          <t>-74,0%</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 2,96</t>
+          <t>-21,18; 2,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,95</t>
+          <t>0,0; 10,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-15,96</t>
+          <t>-15,38</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-68,37%</t>
+          <t>-68,3%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,11; -11,88</t>
+          <t>-32,69; -11,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,03; -10,97</t>
+          <t>-22,25; -11,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -1,39</t>
+          <t>-13,35; -1,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-24,26; -8,81</t>
+          <t>-23,51; -9,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,23; -41,38</t>
+          <t>-85,18; -39,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-88,9; -56,79</t>
+          <t>-88,49; -56,95</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-74,96; -9,8</t>
+          <t>-73,22; -6,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-82,96; -45,4</t>
+          <t>-82,23; -47,18</t>
         </is>
       </c>
     </row>
